--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9849.030000000001</v>
+        <v>9743.629999999999</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6913.62</v>
+        <v>6875.13</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>50566.84</v>
+        <v>50297.69</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>530554.52</v>
+        <v>536407.89</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>531687.75</v>
+        <v>530945.6899999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10007.81</v>
+        <v>9870.66</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>201043.29</v>
+        <v>198579.07</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18123.34</v>
+        <v>17901.2</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>290759.22</v>
+        <v>294072.23</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>33817.25</v>
+        <v>34044.39</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>34791.31</v>
+        <v>35024.99</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>55666.44</v>
+        <v>54989.46</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>36497.24</v>
+        <v>36053.38</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>35146.84</v>
+        <v>34662.36</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>16722.68</v>
+        <v>16696.03</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>38393.22</v>
+        <v>38456.04</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25623.45</v>
+        <v>26232.71</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>19759.86</v>
+        <v>19846.2</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>42396.62</v>
+        <v>42321.72</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>48857.96</v>
+        <v>48811.95</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>45818.31</v>
+        <v>45592.37</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10638.79</v>
+        <v>10708.56</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>73550.39999999999</v>
+        <v>73712.03</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>187725.15</v>
+        <v>185339.03</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>46458.46</v>
+        <v>47308.62</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>61966.29</v>
+        <v>62947.37</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8876.92</v>
+        <v>8745.969999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>30278.25</v>
+        <v>30109.31</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>27275.13</v>
+        <v>26668.95</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>72797.08</v>
+        <v>73440.07000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>46450.67</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>41367.42</v>
+        <v>41437.2</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>46450.67</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>42814.45</v>
+        <v>42819.69</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>57252.51</v>
+        <v>57700.25</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>39422.12</v>
+        <v>39720.2</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8907.370000000001</v>
+        <v>8891.98</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10195.69</v>
+        <v>10231.51</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7692.5</v>
+        <v>7768.58</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>13055.7</v>
+        <v>13106.67</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7466.23</v>
+        <v>7443.22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1725-5837-CM25</t>
+          <t>3232-62-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9743.629999999999</v>
+        <v>32071.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1725-5863-CM25</t>
+          <t>5251-1130-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6875.13</v>
+        <v>25627.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1422825-2004-CM25</t>
+          <t>3082-514-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>69.050.800-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SERVICIOS INTERNET LIMITADA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.409.600-0</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>50297.69</v>
+        <v>7000.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>316-791-CM25</t>
+          <t>1725-5837-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SISTEMAS COMPUTACIONALES S.A.</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>79.560.740-4</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>536407.89</v>
+        <v>9743.629999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>1725-5863-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>530945.6899999999</v>
+        <v>6875.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1702-883-CM25</t>
+          <t>1422825-2004-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.605-6</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SERVICIOS INTERNET LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>77.409.600-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9870.66</v>
+        <v>50297.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>586-637-CM25</t>
+          <t>316-791-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+          <t>INGENIERIA Y SISTEMAS COMPUTACIONALES S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.561.404-k</t>
+          <t>79.560.740-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>198579.07</v>
+        <v>536407.89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>586-675-CM25</t>
+          <t>586-630-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>17901.2</v>
+        <v>530945.6899999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>586-623-CM25</t>
+          <t>1702-883-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.606.605-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>294072.23</v>
+        <v>9870.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3232-798-CM25</t>
+          <t>586-637-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.561.404-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>34044.39</v>
+        <v>198579.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3232-795-CM25</t>
+          <t>586-675-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35024.99</v>
+        <v>17901.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3073-8-CM26</t>
+          <t>586-623-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ARKAVIA NETWORKS SPA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.083.362-2</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>54989.46</v>
+        <v>294072.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2755-6-CM26</t>
+          <t>3232-798-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>36053.38</v>
+        <v>34044.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2755-7-CM26</t>
+          <t>3232-795-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>34662.36</v>
+        <v>35024.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2428-1-CM26</t>
+          <t>3073-8-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>ARKAVIA NETWORKS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.083.362-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>16696.03</v>
+        <v>54989.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4803-25-CM26</t>
+          <t>2755-6-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.046.871-1</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>38456.04</v>
+        <v>36053.38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4301-59-CM26</t>
+          <t>2755-7-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>26232.71</v>
+        <v>34662.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4301-75-CM26</t>
+          <t>2428-1-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>19846.2</v>
+        <v>16696.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1725-79-CM26</t>
+          <t>4803-25-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>76.046.871-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>42321.72</v>
+        <v>38456.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1725-83-CM26</t>
+          <t>4301-59-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>48811.95</v>
+        <v>26232.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1704-1105-CM26</t>
+          <t>4301-75-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>VICTORIA SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>45592.37</v>
+        <v>19846.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1422825-499-CM26</t>
+          <t>1725-79-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10708.56</v>
+        <v>42321.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1704-1310-CM26</t>
+          <t>1725-83-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>73712.03</v>
+        <v>48811.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1035206-191-CM25</t>
+          <t>1704-1105-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>185339.03</v>
+        <v>45592.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1704-1373-CM26</t>
+          <t>1422825-499-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>47308.62</v>
+        <v>10708.56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>548874-73-CM26</t>
+          <t>1704-1310-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.681.168-8</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>62947.37</v>
+        <v>73712.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2170-272-CM26</t>
+          <t>1035206-191-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8745.969999999999</v>
+        <v>185339.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2799-334-CM26</t>
+          <t>1704-1373-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>30109.31</v>
+        <v>47308.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2832-283-CM26</t>
+          <t>548874-73-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>77.681.168-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>26668.95</v>
+        <v>62947.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1725-267-CM26</t>
+          <t>2170-272-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>73440.07000000001</v>
+        <v>8745.969999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1704-2535-CM26</t>
+          <t>2799-334-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>46529.02</v>
+        <v>30109.31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1725-309-CM26</t>
+          <t>2832-283-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>41437.2</v>
+        <v>26668.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1704-2534-CM26</t>
+          <t>1725-267-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>46529.02</v>
+        <v>73440.07000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4301-323-CM26</t>
+          <t>1725-309-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>42819.69</v>
+        <v>41437.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1655-148-CM26</t>
+          <t>1704-2534-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.608.605-7</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>57700.25</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>907581-18-CM26</t>
+          <t>1704-2535-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>39720.2</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3082-271-CM26</t>
+          <t>4301-323-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.050.800-1</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8891.98</v>
+        <v>42819.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1725-541-CM26</t>
+          <t>1655-148-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.608.605-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10231.51</v>
+        <v>57700.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1422825-1197-CM26</t>
+          <t>907581-18-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7768.58</v>
+        <v>39720.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1725-559-CM26</t>
+          <t>3082-271-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.050.800-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.240.269-4</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>13106.67</v>
+        <v>8891.98</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2920-145-CM26</t>
+          <t>1725-541-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,6 +3009,189 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
+        <v>10231.51</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1422825-1197-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>7768.58</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1725-559-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>77.240.269-4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>13106.67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2920-145-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.252.300-8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>MEETCARD</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.437.288-3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
         <v>7443.22</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3232-62-CM25</t>
+          <t>2755-7-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>32071.9</v>
+        <v>29727.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5251-1130-CM25</t>
+          <t>1048-19-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25627.42</v>
+        <v>27693.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3082-514-CM25</t>
+          <t>907581-3-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.050.800-1</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>EXE IOT LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>77.036.438-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7000.22</v>
+        <v>33360.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1725-5837-CM25</t>
+          <t>1057554-51-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>BROWSE INGENIERIA DE SOFTWARE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>79.822.840-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9743.629999999999</v>
+        <v>14715.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1725-5863-CM25</t>
+          <t>3232-62-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6875.13</v>
+        <v>32071.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1422825-2004-CM25</t>
+          <t>1725-4419-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SERVICIOS INTERNET LIMITADA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.409.600-0</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>50297.69</v>
+        <v>56941.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>316-791-CM25</t>
+          <t>586-41-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SISTEMAS COMPUTACIONALES S.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>79.560.740-4</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>536407.89</v>
+        <v>10496.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>1704-134-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>530945.6899999999</v>
+        <v>40838.18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1702-883-CM25</t>
+          <t>3073-107-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.605-6</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>ARKAVIA NETWORKS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.083.362-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9870.66</v>
+        <v>18816.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>586-637-CM25</t>
+          <t>1057554-59-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.561.404-k</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>198579.07</v>
+        <v>55331.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>586-675-CM25</t>
+          <t>2799-193-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>17901.2</v>
+        <v>28861.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>586-623-CM25</t>
+          <t>1704-1019-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>294072.23</v>
+        <v>67581.60000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3232-798-CM25</t>
+          <t>1057554-73-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>34044.39</v>
+        <v>29083.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3232-795-CM25</t>
+          <t>3073-202-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SOCIEDAD LIGARIUS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>77.063.547-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>35024.99</v>
+        <v>10142.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3073-8-CM26</t>
+          <t>1725-4628-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ARKAVIA NETWORKS SPA</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.083.362-2</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>54989.46</v>
+        <v>13976.96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2755-6-CM26</t>
+          <t>1048-195-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>36053.38</v>
+        <v>22149.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2755-7-CM26</t>
+          <t>1725-4780-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.240.269-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>34662.36</v>
+        <v>16727.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2428-1-CM26</t>
+          <t>1725-4779-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>16696.03</v>
+        <v>43194.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4803-25-CM26</t>
+          <t>1725-4774-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
+          <t>ABENIS</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.046.871-1</t>
+          <t>76.217.169-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>38456.04</v>
+        <v>19368.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4301-59-CM26</t>
+          <t>1725-4837-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>TIMIX SERVICE SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.285.037-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>26232.71</v>
+        <v>43293.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4301-75-CM26</t>
+          <t>1704-2933-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>19846.2</v>
+        <v>40467.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1725-79-CM26</t>
+          <t>1704-2935-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>42321.72</v>
+        <v>40467.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1725-83-CM26</t>
+          <t>1725-5031-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>48811.95</v>
+        <v>19605.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1704-1105-CM26</t>
+          <t>1725-5054-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>45592.37</v>
+        <v>30800.23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1422825-499-CM26</t>
+          <t>5300-18-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10708.56</v>
+        <v>50758.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1704-1310-CM26</t>
+          <t>5251-1130-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>73712.03</v>
+        <v>25627.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1035206-191-CM25</t>
+          <t>1725-5116-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>185339.03</v>
+        <v>6674.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1704-1373-CM26</t>
+          <t>1725-5144-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>47308.62</v>
+        <v>20039.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>548874-73-CM26</t>
+          <t>586-289-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.681.168-8</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>62947.37</v>
+        <v>668180.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2170-272-CM26</t>
+          <t>586-411-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>ALFAPEOPLE CHILE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.360.577-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8745.969999999999</v>
+        <v>16969.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2799-334-CM26</t>
+          <t>586-371-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>30109.31</v>
+        <v>232720.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2832-283-CM26</t>
+          <t>586-456-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>26668.95</v>
+        <v>143486.24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1725-267-CM26</t>
+          <t>586-382-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>USERCODE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>77.347.464-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>73440.07000000001</v>
+        <v>143852.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1725-309-CM26</t>
+          <t>1725-5365-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>41437.2</v>
+        <v>25949.03</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1704-2534-CM26</t>
+          <t>3082-514-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.050.800-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>46529.02</v>
+        <v>7000.22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1704-2535-CM26</t>
+          <t>586-404-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>46529.02</v>
+        <v>45751.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4301-323-CM26</t>
+          <t>586-370-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>42819.69</v>
+        <v>151581.75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1655-148-CM26</t>
+          <t>586-402-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.608.605-7</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>57700.25</v>
+        <v>193181.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>907581-18-CM26</t>
+          <t>1375756-79-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.981.270-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.522.707-0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>39720.2</v>
+        <v>20590.82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3082-271-CM26</t>
+          <t>5514-52-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.050.800-1</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8891.98</v>
+        <v>60448.32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1725-541-CM26</t>
+          <t>3775-897-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,27 +2964,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>PAIS DIGITAL SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>77.015.597-5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>10231.51</v>
+        <v>34685.38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1422825-1197-CM26</t>
+          <t>1725-5758-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7768.58</v>
+        <v>11221.66</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1725-559-CM26</t>
+          <t>1725-5837-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.240.269-4</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>13106.67</v>
+        <v>9743.629999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2920-145-CM26</t>
+          <t>1725-5863-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,7 +3192,2752 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
+        <v>6875.13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1422825-2004-CM25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTERNET LIMITADA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>77.409.600-0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>50297.69</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>316-791-CM25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.061.500-2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SISTEMAS COMPUTACIONALES S.A.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>79.560.740-4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>536407.89</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>586-630-CM25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>530945.6899999999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1702-883-CM25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.606.605-6</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>9870.66</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>586-637-CM25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.561.404-k</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>198579.07</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>586-675-CM25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.011.651-3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>17901.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>586-623-CM25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CLOUDHESIVE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.014.934-7</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>294072.23</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3232-795-CM25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.073.500-8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>35024.99</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3232-798-CM25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.073.500-8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SOLNET SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>34044.39</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3073-8-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.102.015-5</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ARKAVIA NETWORKS SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.083.362-2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>54989.46</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2755-6-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.073.400-1</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>36053.38</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2755-7-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.073.400-1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SOLNET SPA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>34662.36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2428-1-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.061.300-K</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>16696.03</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4803-25-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.201.000-7</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SENADO DE LA REPUBLICA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.046.871-1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>38456.04</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4301-59-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SOLNET SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>26232.71</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4301-75-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>VICTORIA SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>19846.2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1725-79-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ANDES DIGITAL</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>42321.72</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1725-83-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>48811.95</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1704-1105-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>45592.37</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1422825-499-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>10708.56</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1704-1310-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>73712.03</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1035206-191-CM25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>65.165.411-4</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>185339.03</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1704-1373-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>47308.62</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>548874-73-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.979.440-0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.681.168-8</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>62947.37</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2170-272-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.606.606-4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>8745.969999999999</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2799-334-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>69.051.100-2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>SOLNET SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>30109.31</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2832-283-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.260.400-8</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>26668.95</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1725-267-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>73440.07000000001</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1704-2534-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>46529.02</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1704-2535-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>46529.02</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1725-309-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ANDES DIGITAL</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>41437.2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4301-323-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SOSAFE</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>42819.69</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1655-148-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.608.605-7</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>GEORG</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>57700.25</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>907581-18-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>39720.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3082-271-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.050.800-1</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>8891.98</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1725-541-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>10231.51</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1422825-1197-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>7768.58</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1725-559-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>77.240.269-4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>13106.67</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2920-145-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>69.252.300-8</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>MEETCARD</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.437.288-3</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
         <v>7443.22</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>701-373-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ANIDA CONSULTORES S A</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>77.680.090-2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>87794.46000000001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1725-703-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>7272.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>586-331-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>CLOUDHESIVE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>77.014.934-7</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>209143.07</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1725-773-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Andes Digital</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>53626.88</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4555-192-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>LUUK SPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>77.363.384-3</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>71485.77</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1725-793-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>14336.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1704-2933-CM25</t>
+          <t>1704-2935-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1704-2935-CM25</t>
+          <t>1704-2933-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4601,7 +4601,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>548874-73-CM26</t>
+          <t>2170-272-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>LDV SERVICIOS PROFESIONALES COMPUTACIONALES LIMITADA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.681.168-8</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>62947.37</v>
+        <v>8745.969999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2170-272-CM26</t>
+          <t>2799-334-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>8745.969999999999</v>
+        <v>30109.31</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2799-334-CM26</t>
+          <t>2832-283-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>30109.31</v>
+        <v>26668.95</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2832-283-CM26</t>
+          <t>1725-267-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>26668.95</v>
+        <v>73440.07000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1725-267-CM26</t>
+          <t>1725-309-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>73440.07000000001</v>
+        <v>41437.2</v>
       </c>
     </row>
     <row r="74">
@@ -5028,7 +5028,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1725-309-CM26</t>
+          <t>4301-323-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,22 +5043,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>41437.2</v>
+        <v>42819.69</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4301-323-CM26</t>
+          <t>907581-18-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>42819.69</v>
+        <v>39720.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1655-148-CM26</t>
+          <t>3082-271-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.608.605-7</t>
+          <t>69.050.800-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>57700.25</v>
+        <v>8891.98</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>907581-18-CM26</t>
+          <t>1725-541-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,27 +5221,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>39720.2</v>
+        <v>10231.51</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3082-271-CM26</t>
+          <t>1422825-1197-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.050.800-1</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>8891.98</v>
+        <v>7768.58</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1725-541-CM26</t>
+          <t>1725-559-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>77.240.269-4</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>10231.51</v>
+        <v>13106.67</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1422825-1197-CM26</t>
+          <t>2920-145-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>69.252.300-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7768.58</v>
+        <v>7443.22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1725-559-CM26</t>
+          <t>701-373-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
+          <t>ANIDA CONSULTORES S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.240.269-4</t>
+          <t>77.680.090-2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>13106.67</v>
+        <v>87794.46000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2920-145-CM26</t>
+          <t>1725-703-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,27 +5526,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>7443.22</v>
+        <v>7272.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>701-373-CM26</t>
+          <t>586-331-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,22 +5592,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ANIDA CONSULTORES S A</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.680.090-2</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>87794.46000000001</v>
+        <v>209143.07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1725-703-CM26</t>
+          <t>1725-773-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7272.5</v>
+        <v>53626.88</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>586-331-CM26</t>
+          <t>4555-192-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,22 +5714,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>LUUK SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>77.363.384-3</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>209143.07</v>
+        <v>71485.77</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1725-773-CM26</t>
+          <t>1725-793-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>53626.88</v>
+        <v>14336.79</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4555-192-CM26</t>
+          <t>2799-861-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>LUUK SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.363.384-3</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>71485.77</v>
+        <v>18196.19</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1725-793-CM26</t>
+          <t>586-410-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>XMS Business Solutions S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.249.938-k</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,7 +5937,190 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>14336.79</v>
+        <v>16165.58</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1725-893-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>7026.13</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>5514-70-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>60.201.000-7</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SENADO DE LA REPUBLICA</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>COMPUNET S.P.A.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>78.466.220-9</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>54656.28</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1725-950-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>22820.37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
@@ -623,7 +623,11 @@
           <t>76.376.088-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.036.438-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1493,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1619,11 @@
           <t>77.714.387-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1684,11 @@
           <t>76.217.169-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1749,11 @@
           <t>77.285.037-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1936,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2001,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2066,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2131,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2196,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2566,11 @@
           <t>77.347.464-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2692,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3062,11 @@
           <t>77.015.597-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3127,11 @@
           <t>77.714.387-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3741,11 @@
           <t>76.516.485-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3928,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4054,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4241,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4489,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4615,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4924,11 @@
           <t>77.714.387-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5172,11 @@
           <t>76.376.088-k</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5237,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5302,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5367,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5432,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5680,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5867,11 @@
           <t>77.363.384-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5932,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5997,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6062,11 @@
           <t>76.249.938-k</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6127,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6253,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -875,7 +875,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1001,7 +1005,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1814,7 +1822,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1875,7 +1887,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2261,7 +2277,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2631,7 +2651,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2892,7 +2916,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1375756-79-CM25</t>
+          <t>5514-52-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2912,17 +2936,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.981.270-0</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2932,12 +2956,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.522.707-0</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2947,13 +2971,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>20590.82</v>
+        <v>60448.32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5514-52-CM25</t>
+          <t>1375756-79-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2973,17 +2997,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>61.981.270-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2993,12 +3017,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.522.707-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -3008,7 +3032,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>60448.32</v>
+        <v>20590.82</v>
       </c>
     </row>
     <row r="42">
@@ -4367,7 +4391,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4428,7 +4456,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4680,7 +4712,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4941,7 +4977,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1725-309-CM26</t>
+          <t>1704-2534-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4961,17 +4997,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4981,28 +5017,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>41437.2</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1704-2534-CM26</t>
+          <t>1704-2535-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5050,7 +5090,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5063,7 +5107,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1704-2535-CM26</t>
+          <t>1725-309-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5083,17 +5127,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5103,12 +5147,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5118,7 +5162,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>46529.02</v>
+        <v>41437.2</v>
       </c>
     </row>
     <row r="76">
@@ -5969,7 +6013,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6034,7 +6078,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6265,6 +6309,258 @@
       </c>
       <c r="M93" s="2" t="n">
         <v>22820.37</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>586-452-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>USERCODE SPA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>77.347.464-8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>64871.73</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1725-973-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>76.444.489-2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>21917.82</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4968-1620-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.606.604-8</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE QUILPUE</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>140115.69</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1725-1050-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>76.213.064-5</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>11282.52</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/valparaiso.xlsx
@@ -4428,7 +4428,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
